--- a/members/P2_Form_BP_Cong_Nghe - Nguyen Dang Duc.xlsx
+++ b/members/P2_Form_BP_Cong_Nghe - Nguyen Dang Duc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CONG VIEC\project-management\members\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0DD4A5-060A-4805-A0BC-7B38FF747451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E97B776-C34D-4349-BFD4-A0517357A0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1023,10 +1023,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1036,89 +1065,57 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1126,6 +1123,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1472,7 +1472,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="30"/>
@@ -1481,7 +1481,7 @@
       <c r="E1" s="30"/>
     </row>
     <row r="3" spans="1:5" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="30"/>
@@ -1490,7 +1490,7 @@
       <c r="E3" s="30"/>
     </row>
     <row r="5" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="43" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="30"/>
@@ -1499,7 +1499,7 @@
       <c r="E5" s="30"/>
     </row>
     <row r="6" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="41" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="30"/>
@@ -1528,7 +1528,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="45" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="30"/>
@@ -1536,111 +1536,111 @@
       <c r="D1" s="30"/>
     </row>
     <row r="3" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
     </row>
     <row r="4" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="64" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
-      <c r="D4" s="35"/>
+      <c r="D4" s="47"/>
     </row>
     <row r="5" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="62" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
-      <c r="D5" s="35"/>
+      <c r="D5" s="47"/>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="27"/>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="51" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="30"/>
-      <c r="D6" s="35"/>
+      <c r="D6" s="47"/>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="27"/>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="51" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="30"/>
-      <c r="D7" s="35"/>
+      <c r="D7" s="47"/>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27"/>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="51" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="30"/>
-      <c r="D8" s="35"/>
+      <c r="D8" s="47"/>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="28"/>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="54"/>
     </row>
     <row r="11" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="43"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="50"/>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27"/>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="51" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="30"/>
-      <c r="D12" s="35"/>
+      <c r="D12" s="47"/>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="28"/>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="46"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="54"/>
     </row>
     <row r="16" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="50"/>
     </row>
     <row r="17" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="69" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
-      <c r="D17" s="35"/>
+      <c r="D17" s="47"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="55" t="s">
+      <c r="A18" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="46"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="54"/>
     </row>
     <row r="19" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="58" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="30"/>
@@ -1648,7 +1648,7 @@
       <c r="D19" s="30"/>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="55" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="30"/>
@@ -1656,7 +1656,7 @@
       <c r="D20" s="30"/>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="55" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="30"/>
@@ -1664,7 +1664,7 @@
       <c r="D21" s="30"/>
     </row>
     <row r="23" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="63" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="30"/>
@@ -1672,82 +1672,82 @@
       <c r="D23" s="30"/>
     </row>
     <row r="24" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="43"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="50"/>
     </row>
     <row r="25" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="27"/>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="46" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="30"/>
-      <c r="D25" s="35"/>
+      <c r="D25" s="47"/>
     </row>
     <row r="26" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="27"/>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="46" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="30"/>
-      <c r="D26" s="35"/>
+      <c r="D26" s="47"/>
     </row>
     <row r="27" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="46"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="54"/>
     </row>
     <row r="29" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="43"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="50"/>
     </row>
     <row r="30" spans="1:4" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="28"/>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="46"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="54"/>
     </row>
     <row r="32" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="43"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="50"/>
     </row>
     <row r="33" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="27"/>
-      <c r="B33" s="52" t="s">
+      <c r="B33" s="46" t="s">
         <v>29</v>
       </c>
       <c r="C33" s="30"/>
-      <c r="D33" s="35"/>
+      <c r="D33" s="47"/>
     </row>
     <row r="34" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="28"/>
-      <c r="B34" s="48" t="s">
+      <c r="B34" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="45"/>
-      <c r="D34" s="46"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="54"/>
     </row>
     <row r="37" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="50"/>
+      <c r="B37" s="61"/>
     </row>
     <row r="38" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
@@ -1791,15 +1791,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="B12:D12"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A19:D19"/>
@@ -1810,12 +1801,21 @@
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B6:D6"/>
@@ -1837,7 +1837,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="29" t="s">
         <v>42</v>
       </c>
       <c r="B1" s="30"/>
@@ -1849,20 +1849,20 @@
       <c r="A3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="37" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="30"/>
       <c r="D3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="60"/>
+      <c r="E3" s="37"/>
     </row>
     <row r="4" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="37" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="30"/>
@@ -1967,7 +1967,7 @@
       <c r="E11" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="34" t="s">
         <v>62</v>
       </c>
       <c r="B13" s="30"/>
@@ -1979,7 +1979,7 @@
       <c r="A14" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="38" t="s">
         <v>64</v>
       </c>
       <c r="C14" s="30"/>
@@ -1990,52 +1990,52 @@
       <c r="A15" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="58"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="33"/>
     </row>
     <row r="16" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="58"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33"/>
     </row>
     <row r="17" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="33"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="21"/>
       <c r="B18" s="22"/>
     </row>
     <row r="21" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="63" t="s">
+      <c r="A21" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="58"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="33"/>
     </row>
     <row r="22" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="58"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="33"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="26"/>
@@ -2085,17 +2085,17 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="65" t="s">
+      <c r="A29" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="58"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
     </row>
     <row r="30" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B30" s="59">
+      <c r="B30" s="35">
         <f>IF(COUNTA(C25:C27)=0,"",
 AVERAGE(
  IF(C25="Chưa đạt",1.5,IF(C25="Đạt",3.5,IF(C25="Tốt",5,""))),
@@ -2104,17 +2104,17 @@
 ))</f>
         <v>3.5</v>
       </c>
-      <c r="C30" s="58"/>
+      <c r="C30" s="33"/>
     </row>
     <row r="31" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="59">
+      <c r="B31" s="35">
         <f>IF(OR(D11="",B30=""),"",D11*0.5+B30*0.5)</f>
         <v>3.4874999999999998</v>
       </c>
-      <c r="C31" s="58"/>
+      <c r="C31" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2191,7 +2191,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="66" t="s">
         <v>80</v>
       </c>
       <c r="B1" s="30"/>
@@ -2199,7 +2199,7 @@
       <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="68" t="s">
         <v>81</v>
       </c>
       <c r="B2" s="30"/>
@@ -2207,7 +2207,7 @@
       <c r="D2" s="30"/>
     </row>
     <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="67" t="s">
         <v>82</v>
       </c>
       <c r="B4" s="30"/>
@@ -2285,7 +2285,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="67" t="s">
         <v>100</v>
       </c>
       <c r="B11" s="30"/>
@@ -2363,7 +2363,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="67" t="s">
         <v>113</v>
       </c>
       <c r="B18" s="30"/>
@@ -2441,7 +2441,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="68" t="s">
+      <c r="A25" s="67" t="s">
         <v>126</v>
       </c>
       <c r="B25" s="30"/>
@@ -2554,7 +2554,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="29" t="s">
         <v>139</v>
       </c>
       <c r="B1" s="30"/>
@@ -2566,7 +2566,7 @@
       <c r="H1" s="30"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="37" t="s">
         <v>140</v>
       </c>
       <c r="B3" s="30"/>
